--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/11_risks_controls.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/11_risks_controls.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R22ea45673f534fb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rb41aa177f00b4e0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R8cef27150ffc4a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Ra7748f4ceda6414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R05afed94a3b8428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R58ec63cc611e499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R20ce2ab6ff3d4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R2d579a1f0fed4129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R399f0e953f9f4de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Re78b553dd78e4b3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8cc7ef34826f4b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rb1ba3b97f2b3493c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd04d190a6f9044f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R222b20e5fc224fdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -785,7 +785,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="M6" s="78" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Executive Office data lineage and definition risk (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N6" s="41" t="str">
         <x:v>High</x:v>
@@ -829,7 +829,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV02</x:v>
       </x:c>
       <x:c r="M7" s="79" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Executive Office operational resilience and change risk (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -873,7 +873,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Retail Deposits and Branch Operations data lineage and definition risk (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N8" t="str">
         <x:v>High</x:v>
@@ -917,7 +917,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV02</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Retail Deposits and Branch Operations operational resilience and change risk (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N9" t="str">
         <x:v>Medium</x:v>
@@ -961,7 +961,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury data lineage and definition risk (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N10" t="str">
         <x:v>High</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV02</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Commercial Lending and Treasury operational resilience and change risk (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>Medium</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Cards Operations data lineage and definition risk (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N12" t="str">
         <x:v>High</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV02</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Cards Operations operational resilience and change risk (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N13" t="str">
         <x:v>Medium</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Payments Operations data lineage and definition risk (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>High</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV02</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations operational resilience and change risk (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N15" t="str">
         <x:v>Medium</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Consumer Lending Operations data lineage and definition risk (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N16" t="str">
         <x:v>High</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV02</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Consumer Lending Operations operational resilience and change risk (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N17" t="str">
         <x:v>Medium</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory and Brokerage data lineage and definition risk (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N18" t="str">
         <x:v>High</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV02</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage operational resilience and change risk (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N19" t="str">
         <x:v>Medium</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>Data quality / lineage / reporting</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Definitions, lineage, and certification gaps could cause Fraud and Risk Operations decisions to rely on inconsistent or stale context.</x:v>
+        <x:v>Fraud Analyst Copilot risk: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>Fraud and Risk Operations</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>Catalog source ownership, reconcile critical measures, certify data products, and expose gaps before module handoff.</x:v>
+        <x:v>Validate Fraud feature store design notes with feedback-loop and model governance gaps.; implement control around queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>Control design needed</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Fraud and Risk Operations data lineage and definition risk (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>High</x:v>
@@ -1415,7 +1415,7 @@
         <x:v>Operational resilience / change control</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Incidents, batch failures, interface breaks, or change collisions can degrade fraud alerts, case triage, AML/transaction monitoring, loss prevention.</x:v>
+        <x:v>Fraud Analyst Copilot risk: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>Fraud and Risk Operations</x:v>
@@ -1433,7 +1433,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Link incidents/problems/changes to systems, owners, SLAs, and Tower metrics.</x:v>
+        <x:v>Validate Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; implement control around case outcome feedback gaps.</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Partially evidenced from synthetic adapter rows</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV02</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Fraud and Risk Operations operational resilience and change risk (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N21" t="str">
         <x:v>Medium</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management data lineage and definition risk (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N22" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV02</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management operational resilience and change risk (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N23" t="str">
         <x:v>Medium</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Contact Center and Servicing data lineage and definition risk (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>High</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV02</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing operational resilience and change risk (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N25" t="str">
         <x:v>Medium</x:v>
@@ -1665,7 +1665,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding data lineage and definition risk (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N26" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV02</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Digital Account Opening and Onboarding operational resilience and change risk (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N27" t="str">
         <x:v>Medium</x:v>
@@ -1753,7 +1753,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="M28" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization data lineage and definition risk (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N28" t="str">
         <x:v>High</x:v>
@@ -1797,7 +1797,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV02</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Core Banking Modernization operational resilience and change risk (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N29" t="str">
         <x:v>Medium</x:v>
@@ -1841,7 +1841,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="M30" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product data lineage and definition risk (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N30" t="str">
         <x:v>High</x:v>
@@ -1885,7 +1885,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV02</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Customer 360 Data Product operational resilience and change risk (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N31" t="str">
         <x:v>Medium</x:v>
@@ -1929,7 +1929,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="M32" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Retail Banking Analytics data lineage and definition risk (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N32" t="str">
         <x:v>High</x:v>
@@ -1973,7 +1973,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="M33" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics operational resilience and change risk (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N33" t="str">
         <x:v>Medium</x:v>
@@ -2017,7 +2017,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="M34" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics data lineage and definition risk (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N34" t="str">
         <x:v>High</x:v>
@@ -2061,7 +2061,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="M35" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics operational resilience and change risk (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N35" t="str">
         <x:v>Medium</x:v>
@@ -2105,7 +2105,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="M36" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Payments and Settlement Analytics data lineage and definition risk (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N36" t="str">
         <x:v>High</x:v>
@@ -2149,7 +2149,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics operational resilience and change risk (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N37" t="str">
         <x:v>Medium</x:v>
@@ -2163,7 +2163,7 @@
         <x:v>Data quality / lineage / reporting</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Definitions, lineage, and certification gaps could cause Fraud and Risk Analytics decisions to rely on inconsistent or stale context.</x:v>
+        <x:v>Fraud Analyst Copilot risk: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="D38" t="str">
         <x:v>Fraud and Risk Analytics</x:v>
@@ -2181,7 +2181,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>Catalog source ownership, reconcile critical measures, certify data products, and expose gaps before module handoff.</x:v>
+        <x:v>Validate AML transaction monitoring source inventory and control-owner interview.; implement control around queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="J38" t="str">
         <x:v>Control design needed</x:v>
@@ -2193,7 +2193,7 @@
         <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Fraud and Risk Analytics data lineage and definition risk (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N38" t="str">
         <x:v>High</x:v>
@@ -2207,7 +2207,7 @@
         <x:v>Operational resilience / change control</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Incidents, batch failures, interface breaks, or change collisions can degrade fraud scores, alert productivity, loss trends, risk segmentation.</x:v>
+        <x:v>Fraud Analyst Copilot risk: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="D39" t="str">
         <x:v>Fraud and Risk Analytics</x:v>
@@ -2225,7 +2225,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I39" t="str">
-        <x:v>Link incidents/problems/changes to systems, owners, SLAs, and Tower metrics.</x:v>
+        <x:v>Validate Digital onboarding/KYC vendor report with identity verification and device-risk signals.; implement control around case outcome feedback gaps.</x:v>
       </x:c>
       <x:c r="J39" t="str">
         <x:v>Partially evidenced from synthetic adapter rows</x:v>
@@ -2237,7 +2237,7 @@
         <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="M39" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Fraud and Risk Analytics operational resilience and change risk (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N39" t="str">
         <x:v>Medium</x:v>
@@ -2281,7 +2281,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="M40" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform data lineage and definition risk (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N40" t="str">
         <x:v>High</x:v>
@@ -2325,7 +2325,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV02</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Cloud Data Platform operational resilience and change risk (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N41" t="str">
         <x:v>Medium</x:v>
@@ -2369,7 +2369,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="M42" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline data lineage and definition risk (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N42" t="str">
         <x:v>High</x:v>
@@ -2413,7 +2413,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV02</x:v>
       </x:c>
       <x:c r="M43" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline operational resilience and change risk (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N43" t="str">
         <x:v>Medium</x:v>
@@ -2457,7 +2457,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="M44" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization data lineage and definition risk (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N44" t="str">
         <x:v>High</x:v>
@@ -2501,7 +2501,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV02</x:v>
       </x:c>
       <x:c r="M45" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization operational resilience and change risk (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N45" t="str">
         <x:v>Medium</x:v>
@@ -2545,7 +2545,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="M46" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Infrastructure and CMDB data lineage and definition risk (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N46" t="str">
         <x:v>High</x:v>
@@ -2589,7 +2589,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV02</x:v>
       </x:c>
       <x:c r="M47" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Infrastructure and CMDB operational resilience and change risk (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N47" t="str">
         <x:v>Medium</x:v>
@@ -2633,7 +2633,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="M48" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations data lineage and definition risk (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N48" t="str">
         <x:v>High</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV02</x:v>
       </x:c>
       <x:c r="M49" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations operational resilience and change risk (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N49" t="str">
         <x:v>Medium</x:v>
@@ -2704,7 +2704,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R017c29ce5e3d464f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra266f8b7768d45af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2779,7 +2779,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra44618e23c4c472c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f98103d60e64da2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2953,7 +2953,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3295126cb542db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0e4a02b5f94610"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3031,7 +3031,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re753985416224ab2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b9e457eb8243c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3141,7 +3141,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5ad6187d454e8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4362ada8eae448ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>